--- a/Belgian_Pro_League_Ratings_2019_2024_Complete.xlsx
+++ b/Belgian_Pro_League_Ratings_2019_2024_Complete.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P52\Documents\Master Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5D40A28D-1351-4949-9AE3-EC5D6742B035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7933E47D-51FE-4BF5-9949-9AF2150EB44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0AF966E-A913-4F4D-92B9-457C3E2721E6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0AF966E-A913-4F4D-92B9-457C3E2721E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Belgian_Pro_League_Ratings_2019" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Belgian_Pro_League_Ratings_2019!$A$1:$H$80</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="41">
   <si>
     <t>Team</t>
   </si>
@@ -55,42 +58,12 @@
     <t>2019-2020</t>
   </si>
   <si>
-    <t>KAA Gent</t>
-  </si>
-  <si>
-    <t>Standard LiÃ¨ge</t>
-  </si>
-  <si>
     <t>Fast Build-Up</t>
   </si>
   <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>KRC Genk</t>
-  </si>
-  <si>
-    <t>Royal Antwerp</t>
-  </si>
-  <si>
     <t>Long Ball</t>
   </si>
   <si>
-    <t>Sporting Charleroi</t>
-  </si>
-  <si>
-    <t>KV Mechelen</t>
-  </si>
-  <si>
-    <t>Zulte Waregem</t>
-  </si>
-  <si>
-    <t>KV Oostende</t>
-  </si>
-  <si>
-    <t>Sint-Truiden</t>
-  </si>
-  <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
@@ -127,40 +100,52 @@
     <t>Gent</t>
   </si>
   <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
     <t>Mechelen</t>
   </si>
   <si>
     <t>Westerlo</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>RWDM</t>
-  </si>
-  <si>
-    <t>AS Eupen</t>
-  </si>
-  <si>
     <t>Kortrijk</t>
   </si>
   <si>
     <t>2022-2023</t>
   </si>
   <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>RFC Seraing</t>
-  </si>
-  <si>
     <t>2021-2022</t>
   </si>
   <si>
-    <t>Beerschot</t>
+    <t>Beerschot VA</t>
+  </si>
+  <si>
+    <t>Slow Build up</t>
+  </si>
+  <si>
+    <t>Oostende</t>
+  </si>
+  <si>
+    <t>Oud-Heverlee Leuven</t>
+  </si>
+  <si>
+    <t>St Truiden</t>
+  </si>
+  <si>
+    <t>Charleroi</t>
+  </si>
+  <si>
+    <t>RWD Molenbeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard </t>
+  </si>
+  <si>
+    <t>Waregem</t>
+  </si>
+  <si>
+    <t>St. Gilloise</t>
+  </si>
+  <si>
+    <t>Seraing</t>
   </si>
 </sst>
 </file>
@@ -644,8 +629,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1021,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DD1CCB-D3F3-4B67-8F64-4C258136C52C}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" customWidth="1"/>
@@ -1062,77 +1050,77 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C2">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D2">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F2">
         <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B3">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D3">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E3">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4">
         <v>71</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
@@ -1140,16 +1128,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>71</v>
@@ -1161,82 +1149,82 @@
         <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
         <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7">
+        <v>72</v>
+      </c>
+      <c r="C7">
+        <v>72</v>
+      </c>
+      <c r="D7">
+        <v>72</v>
+      </c>
+      <c r="E7">
         <v>71</v>
       </c>
-      <c r="C7">
-        <v>72</v>
-      </c>
-      <c r="D7">
-        <v>71</v>
-      </c>
-      <c r="E7">
-        <v>70</v>
-      </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>72</v>
+      </c>
+      <c r="D8">
+        <v>71</v>
+      </c>
+      <c r="E8">
         <v>70</v>
       </c>
-      <c r="C8">
-        <v>71</v>
-      </c>
-      <c r="D8">
-        <v>70</v>
-      </c>
-      <c r="E8">
-        <v>69</v>
-      </c>
       <c r="F8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
@@ -1244,54 +1232,54 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C9">
+        <v>73</v>
+      </c>
+      <c r="D9">
+        <v>72</v>
+      </c>
+      <c r="E9">
         <v>70</v>
       </c>
-      <c r="D9">
-        <v>69</v>
-      </c>
-      <c r="E9">
-        <v>68</v>
-      </c>
       <c r="F9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C10">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -1299,68 +1287,68 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C11">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D11">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E11">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F11">
         <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C12">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D12">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E12">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F12">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B13">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13">
         <v>67</v>
       </c>
       <c r="D13">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13">
         <v>25</v>
@@ -1369,30 +1357,30 @@
         <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B14">
+        <v>66</v>
+      </c>
+      <c r="C14">
+        <v>67</v>
+      </c>
+      <c r="D14">
+        <v>66</v>
+      </c>
+      <c r="E14">
         <v>65</v>
       </c>
-      <c r="C14">
-        <v>66</v>
-      </c>
-      <c r="D14">
-        <v>65</v>
-      </c>
-      <c r="E14">
-        <v>64</v>
-      </c>
       <c r="F14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
         <v>10</v>
@@ -1400,377 +1388,377 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <v>68</v>
+      </c>
+      <c r="D15">
+        <v>67</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+      <c r="F15">
         <v>25</v>
       </c>
-      <c r="B15">
-        <v>65</v>
-      </c>
-      <c r="C15">
-        <v>65</v>
-      </c>
-      <c r="D15">
-        <v>65</v>
-      </c>
-      <c r="E15">
-        <v>64</v>
-      </c>
-      <c r="F15">
-        <v>26</v>
-      </c>
       <c r="G15" t="s">
         <v>9</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E16">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B17">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D17">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E17">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B18">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C18">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D18">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E18">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C19">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D19">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E19">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D20">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E20">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F20">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E21">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
         <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B22">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C22">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D22">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E22">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F22">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B23">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C23">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D23">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E23">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H23" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B24">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C24">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D24">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E24">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
         <v>9</v>
       </c>
       <c r="H24" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>75</v>
+      </c>
+      <c r="E25">
+        <v>71</v>
+      </c>
+      <c r="F25">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
         <v>20</v>
       </c>
-      <c r="B25">
-        <v>69</v>
-      </c>
-      <c r="C25">
-        <v>70</v>
-      </c>
-      <c r="D25">
-        <v>69</v>
-      </c>
-      <c r="E25">
-        <v>67</v>
-      </c>
-      <c r="F25">
-        <v>28</v>
-      </c>
-      <c r="G25" t="s">
-        <v>9</v>
-      </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B26">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C26">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D26">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E26">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F26">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B27">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C27">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D27">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E27">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F27">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B28">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D28">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E28">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" t="s">
         <v>9</v>
       </c>
       <c r="H28" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B29">
         <v>66</v>
       </c>
       <c r="C29">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D29">
         <v>66</v>
@@ -1779,82 +1767,82 @@
         <v>64</v>
       </c>
       <c r="F29">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G29" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" t="s">
         <v>17</v>
-      </c>
-      <c r="H29" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B30">
+        <v>67</v>
+      </c>
+      <c r="C30">
+        <v>67</v>
+      </c>
+      <c r="D30">
+        <v>67</v>
+      </c>
+      <c r="E30">
         <v>66</v>
       </c>
-      <c r="C30">
-        <v>66</v>
-      </c>
-      <c r="D30">
-        <v>66</v>
-      </c>
-      <c r="E30">
-        <v>64</v>
-      </c>
       <c r="F30">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B31">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D31">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E31">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B32">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C32">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D32">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E32">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F32">
         <v>28</v>
@@ -1868,59 +1856,59 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B33">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C33">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E33">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F33">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H33" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B34">
         <v>73</v>
       </c>
       <c r="C34">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34">
         <v>73</v>
       </c>
       <c r="E34">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F34">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>72</v>
@@ -1938,24 +1926,24 @@
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B36">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C36">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E36">
         <v>72</v>
@@ -1964,30 +1952,30 @@
         <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B37">
         <v>72</v>
       </c>
       <c r="C37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D37">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E37">
         <v>72</v>
       </c>
       <c r="F37">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G37" t="s">
         <v>9</v>
@@ -1998,149 +1986,146 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B38">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D38">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E38">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F38">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38" t="s">
         <v>9</v>
       </c>
       <c r="H38" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B39">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C39">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D39">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E39">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F39">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G39" t="s">
         <v>9</v>
       </c>
       <c r="H39" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B40">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C40">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D40">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E40">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F40">
         <v>28</v>
       </c>
       <c r="G40" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H40" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>23</v>
+      <c r="A41" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B41">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C41">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E41">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F41">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H41" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42">
-        <v>68</v>
+      <c r="A42" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C42">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D42">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E42">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F42">
         <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B43">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>67</v>
       </c>
       <c r="D43">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E43">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -2149,24 +2134,24 @@
         <v>9</v>
       </c>
       <c r="H43" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B44">
         <v>68</v>
       </c>
       <c r="C44">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D44">
         <v>68</v>
       </c>
       <c r="E44">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F44">
         <v>28</v>
@@ -2175,24 +2160,24 @@
         <v>9</v>
       </c>
       <c r="H44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B45">
+        <v>68</v>
+      </c>
+      <c r="C45">
         <v>67</v>
       </c>
-      <c r="C45">
-        <v>70</v>
-      </c>
       <c r="D45">
         <v>68</v>
       </c>
       <c r="E45">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F45">
         <v>28</v>
@@ -2206,71 +2191,71 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B46">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C46">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D46">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E46">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F46">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H46" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B47">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C47">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D47">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E47">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F47">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G47" t="s">
         <v>9</v>
       </c>
       <c r="H47" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C48">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D48">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E48">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F48">
         <v>28</v>
@@ -2279,24 +2264,24 @@
         <v>9</v>
       </c>
       <c r="H48" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B49">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C49">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D49">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E49">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F49">
         <v>28</v>
@@ -2305,24 +2290,24 @@
         <v>9</v>
       </c>
       <c r="H49" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B50">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C50">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D50">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E50">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F50">
         <v>27</v>
@@ -2331,541 +2316,541 @@
         <v>9</v>
       </c>
       <c r="H50" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B51">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C51">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D51">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E51">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F51">
         <v>25</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H51" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B52">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C52">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D52">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E52">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F52">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G52" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B53">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C53">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D53">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E53">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F53">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H53" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B54">
+        <v>68</v>
+      </c>
+      <c r="C54">
         <v>69</v>
       </c>
-      <c r="C54">
-        <v>70</v>
-      </c>
       <c r="D54">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E54">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F54">
         <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H54" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B55">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D55">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E55">
         <v>66</v>
       </c>
       <c r="F55">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B56">
         <v>69</v>
       </c>
       <c r="C56">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D56">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E56">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F56">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B57">
+        <v>68</v>
+      </c>
+      <c r="C57">
         <v>69</v>
       </c>
-      <c r="C57">
-        <v>74</v>
-      </c>
       <c r="D57">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E57">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F57">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H57" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B58">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C58">
+        <v>74</v>
+      </c>
+      <c r="D58">
         <v>70</v>
       </c>
-      <c r="D58">
-        <v>68</v>
-      </c>
       <c r="E58">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F58">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G58" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B59">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C59">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D59">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E59">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F59">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G59" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B60">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D60">
         <v>68</v>
       </c>
       <c r="E60">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F60">
         <v>28</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H60" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B61">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61">
+        <v>67</v>
+      </c>
+      <c r="D61">
+        <v>67</v>
+      </c>
+      <c r="E61">
         <v>66</v>
       </c>
-      <c r="D61">
-        <v>68</v>
-      </c>
-      <c r="E61">
-        <v>65</v>
-      </c>
       <c r="F61">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H61" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B62">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C62">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D62">
         <v>68</v>
       </c>
       <c r="E62">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F62">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H62" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B63">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C63">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D63">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E63">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F63">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H63" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B64">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C64">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D64">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E64">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F64">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G64" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H64" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B65">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C65">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D65">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E65">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F65">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H65" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B66">
         <v>72</v>
       </c>
       <c r="C66">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D66">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E66">
         <v>72</v>
       </c>
       <c r="F66">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66" t="s">
         <v>9</v>
       </c>
       <c r="H66" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B67">
+        <v>72</v>
+      </c>
+      <c r="C67">
         <v>71</v>
       </c>
-      <c r="C67">
-        <v>74</v>
-      </c>
       <c r="D67">
+        <v>73</v>
+      </c>
+      <c r="E67">
         <v>71</v>
       </c>
-      <c r="E67">
-        <v>70</v>
-      </c>
       <c r="F67">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B68">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C68">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D68">
+        <v>71</v>
+      </c>
+      <c r="E68">
         <v>70</v>
       </c>
-      <c r="E68">
-        <v>69</v>
-      </c>
       <c r="F68">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H68" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B69">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C69">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D69">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E69">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F69">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H69" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B70">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C70">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D70">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E70">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F70">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H70" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B71">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C71">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D71">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E71">
         <v>69</v>
@@ -2877,129 +2862,129 @@
         <v>9</v>
       </c>
       <c r="H71" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72">
         <v>69</v>
       </c>
       <c r="C72">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D72">
         <v>70</v>
       </c>
       <c r="E72">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F72">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H72" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B73">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C73">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D73">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E73">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F73">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H73" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B74">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C74">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D74">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E74">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F74">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G74" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H74" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B75">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C75">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D75">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E75">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F75">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G75" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H75" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B76">
         <v>68</v>
       </c>
       <c r="C76">
+        <v>69</v>
+      </c>
+      <c r="D76">
+        <v>68</v>
+      </c>
+      <c r="E76">
         <v>67</v>
       </c>
-      <c r="D76">
-        <v>68</v>
-      </c>
-      <c r="E76">
-        <v>69</v>
-      </c>
       <c r="F76">
         <v>28</v>
       </c>
@@ -3007,51 +2992,51 @@
         <v>9</v>
       </c>
       <c r="H76" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B77">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C77">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D77">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E77">
         <v>67</v>
       </c>
       <c r="F77">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G77" t="s">
         <v>9</v>
       </c>
       <c r="H77" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B78">
+        <v>68</v>
+      </c>
+      <c r="C78">
+        <v>70</v>
+      </c>
+      <c r="D78">
+        <v>68</v>
+      </c>
+      <c r="E78">
         <v>66</v>
       </c>
-      <c r="C78">
-        <v>68</v>
-      </c>
-      <c r="D78">
-        <v>65</v>
-      </c>
-      <c r="E78">
-        <v>65</v>
-      </c>
       <c r="F78">
         <v>28</v>
       </c>
@@ -3059,10 +3044,75 @@
         <v>9</v>
       </c>
       <c r="H78" t="s">
-        <v>45</v>
-      </c>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79">
+        <v>69</v>
+      </c>
+      <c r="C79">
+        <v>70</v>
+      </c>
+      <c r="D79">
+        <v>69</v>
+      </c>
+      <c r="E79">
+        <v>68</v>
+      </c>
+      <c r="F79">
+        <v>28</v>
+      </c>
+      <c r="G79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80">
+        <v>68</v>
+      </c>
+      <c r="C80">
+        <v>67</v>
+      </c>
+      <c r="D80">
+        <v>67</v>
+      </c>
+      <c r="E80">
+        <v>68</v>
+      </c>
+      <c r="F80">
+        <v>28</v>
+      </c>
+      <c r="G80" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H80" xr:uid="{68DD1CCB-D3F3-4B67-8F64-4C258136C52C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H85">
+    <sortCondition ref="A82:A85"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>